--- a/SGI_Sistema-de-gestao-integrado/SGE_Sistema-de-gestao-da-energia/Registos_SGE_Plasticom/SGE-04_Revisao_Energetica_USE.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGE_Sistema-de-gestao-da-energia/Registos_SGE_Plasticom/SGE-04_Revisao_Energetica_USE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGE_Sistema-de-gestao-da-energia\Registos_SGE_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBFC9DA-A744-46B5-8C4E-19A87EC72DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D41F8B3-EFFC-4DF6-A830-B62F84C18439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1594,7 +1594,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2853" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2857" uniqueCount="600">
   <si>
     <t>RG-SGE-04 — Revisão Energética e Usos Significativos de Energia</t>
   </si>
@@ -2184,7 +2184,7 @@
     <t>Injeção de tampas e potes: aquecimento do canhão, hidráulica/servo, extração</t>
   </si>
   <si>
-    <t>IM-001 a IM-008</t>
+    <t>IM-001 a IM-009</t>
   </si>
   <si>
     <t>AA-007</t>
@@ -2479,6 +2479,12 @@
   </si>
   <si>
     <t>IM-008</t>
+  </si>
+  <si>
+    <t>IM-009</t>
+  </si>
+  <si>
+    <t>Injetora totalmente elétrica (linha dedicada a contacto alimentar)</t>
   </si>
   <si>
     <t>SS-001</t>
@@ -3843,7 +3849,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4BAE-46C8-AC1E-BD1BDC7D2F1E}"/>
+              <c16:uniqueId val="{00000000-C6A5-43A3-879E-556E2D9551DA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4052,8 +4058,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="tbl_campanha" displayName="tbl_campanha" ref="A4:S26">
-  <autoFilter ref="A4:S26" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="tbl_campanha" displayName="tbl_campanha" ref="A4:S27">
+  <autoFilter ref="A4:S27" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="ID_Maquina"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Processo"/>
@@ -4880,12 +4886,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
@@ -4896,19 +4902,19 @@
         <v>135</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4935,7 +4941,7 @@
         <v>3485586.8550000004</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4962,7 +4968,7 @@
         <v>2136246.8550000004</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -4989,7 +4995,7 @@
         <v>1004098.4100000001</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5016,7 +5022,7 @@
         <v>468146.40000000008</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5043,7 +5049,7 @@
         <v>505147.68000000005</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5070,7 +5076,7 @@
         <v>145555.19500000001</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5097,7 +5103,7 @@
         <v>99237.434999999998</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5124,7 +5130,7 @@
         <v>32091</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5151,12 +5157,12 @@
         <v>2185</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B15" s="27">
         <f>SUM(B5:B13)</f>
@@ -5198,15 +5204,15 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -5219,10 +5225,10 @@
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C4" s="33"/>
       <c r="D4" s="33"/>
@@ -5235,10 +5241,10 @@
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
@@ -5251,10 +5257,10 @@
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
@@ -5267,10 +5273,10 @@
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="33"/>
@@ -5283,10 +5289,10 @@
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
@@ -5299,10 +5305,10 @@
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C9" s="33"/>
       <c r="D9" s="33"/>
@@ -5315,10 +5321,10 @@
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C10" s="33"/>
       <c r="D10" s="33"/>
@@ -5331,10 +5337,10 @@
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -5376,27 +5382,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C2" s="29" t="s">
         <v>181</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F2" s="29" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -5404,16 +5410,16 @@
         <v>46387</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>164</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F3" s="6">
         <v>1</v>
@@ -5421,16 +5427,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>167</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F4" s="6">
         <v>2</v>
@@ -5438,16 +5444,16 @@
     </row>
     <row r="5" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>168</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F5" s="6">
         <v>3</v>
@@ -5455,35 +5461,35 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>169</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>170</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>171</v>
@@ -5491,7 +5497,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>172</v>
@@ -5499,7 +5505,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>173</v>
@@ -5507,7 +5513,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>176</v>
@@ -5515,67 +5521,67 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -5601,16 +5607,16 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>128</v>
@@ -5619,13 +5625,13 @@
         <v>104</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -5633,26 +5639,26 @@
         <v>50</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C2" s="31" t="s">
         <v>101</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I2" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -5660,19 +5666,19 @@
         <v>50</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C3" s="31" t="s">
         <v>102</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G3" s="31"/>
       <c r="H3" s="31" t="s">
@@ -5685,19 +5691,19 @@
         <v>50</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C4" s="31" t="s">
         <v>103</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G4" s="31"/>
       <c r="H4" s="31" t="s">
@@ -5710,19 +5716,19 @@
         <v>50</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>104</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G5" s="31"/>
       <c r="H5" s="31" t="s">
@@ -5735,19 +5741,19 @@
         <v>50</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C6" s="31" t="s">
         <v>105</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G6" s="31"/>
       <c r="H6" s="31" t="s">
@@ -5760,26 +5766,26 @@
         <v>52</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>126</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G7" s="31"/>
       <c r="H7" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -5787,19 +5793,19 @@
         <v>52</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>127</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G8" s="31"/>
       <c r="H8" s="31" t="s">
@@ -5812,19 +5818,19 @@
         <v>52</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>128</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G9" s="31"/>
       <c r="H9" s="31" t="s">
@@ -5837,19 +5843,19 @@
         <v>52</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>129</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G10" s="31"/>
       <c r="H10" s="31" t="s">
@@ -5862,23 +5868,23 @@
         <v>52</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C11" s="31" t="s">
         <v>130</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G11" s="31"/>
       <c r="H11" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I11" s="31"/>
     </row>
@@ -5887,23 +5893,23 @@
         <v>52</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>131</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="G12" s="31"/>
       <c r="H12" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I12" s="31"/>
     </row>
@@ -5912,23 +5918,23 @@
         <v>52</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>132</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G13" s="31"/>
       <c r="H13" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I13" s="31"/>
     </row>
@@ -5937,23 +5943,23 @@
         <v>52</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>133</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G14" s="31"/>
       <c r="H14" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I14" s="31"/>
     </row>
@@ -5962,19 +5968,19 @@
         <v>52</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>134</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="31" t="s">
@@ -5987,19 +5993,19 @@
         <v>52</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>135</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G16" s="31"/>
       <c r="H16" s="31" t="s">
@@ -6012,19 +6018,19 @@
         <v>52</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>136</v>
       </c>
       <c r="D17" s="31" t="s">
+        <v>500</v>
+      </c>
+      <c r="E17" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="E17" s="31" t="s">
-        <v>496</v>
-      </c>
       <c r="F17" s="31" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G17" s="31"/>
       <c r="H17" s="31" t="s">
@@ -6037,19 +6043,19 @@
         <v>52</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>137</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G18" s="31"/>
       <c r="H18" s="31" t="s">
@@ -6062,26 +6068,26 @@
         <v>54</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>161</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G19" s="31"/>
       <c r="H19" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I19" s="31" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -6089,28 +6095,28 @@
         <v>54</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>162</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H20" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I20" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
@@ -6118,26 +6124,26 @@
         <v>54</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>126</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G21" s="31"/>
       <c r="H21" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I21" s="31" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -6145,19 +6151,19 @@
         <v>54</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>141</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G22" s="31"/>
       <c r="H22" s="31" t="s">
@@ -6170,19 +6176,19 @@
         <v>54</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C23" s="31" t="s">
         <v>105</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G23" s="31"/>
       <c r="H23" s="31" t="s">
@@ -6195,19 +6201,19 @@
         <v>54</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C24" s="31" t="s">
         <v>163</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G24" s="31"/>
       <c r="H24" s="31" t="s">
@@ -6220,26 +6226,26 @@
         <v>56</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C25" s="31" t="s">
         <v>162</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I25" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -6247,19 +6253,19 @@
         <v>56</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C26" s="31" t="s">
         <v>181</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31" t="s">
@@ -6272,19 +6278,19 @@
         <v>56</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C27" s="31" t="s">
         <v>127</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G27" s="31"/>
       <c r="H27" s="31" t="s">
@@ -6297,19 +6303,19 @@
         <v>56</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C28" s="31" t="s">
         <v>182</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G28" s="31"/>
       <c r="H28" s="31" t="s">
@@ -6322,19 +6328,19 @@
         <v>56</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C29" s="31" t="s">
         <v>135</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G29" s="31"/>
       <c r="H29" s="31" t="s">
@@ -6347,19 +6353,19 @@
         <v>56</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C30" s="31" t="s">
         <v>183</v>
       </c>
       <c r="D30" s="31" t="s">
+        <v>500</v>
+      </c>
+      <c r="E30" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="E30" s="31" t="s">
-        <v>496</v>
-      </c>
       <c r="F30" s="31" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G30" s="31"/>
       <c r="H30" s="31" t="s">
@@ -6372,19 +6378,19 @@
         <v>56</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C31" s="31" t="s">
         <v>184</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G31" s="31"/>
       <c r="H31" s="31" t="s">
@@ -6397,19 +6403,19 @@
         <v>56</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C32" s="31" t="s">
         <v>185</v>
       </c>
       <c r="D32" s="31" t="s">
+        <v>500</v>
+      </c>
+      <c r="E32" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="E32" s="31" t="s">
-        <v>496</v>
-      </c>
       <c r="F32" s="31" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G32" s="31"/>
       <c r="H32" s="31" t="s">
@@ -6422,19 +6428,19 @@
         <v>56</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C33" s="31" t="s">
         <v>186</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G33" s="31"/>
       <c r="H33" s="31" t="s">
@@ -6447,19 +6453,19 @@
         <v>56</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C34" s="31" t="s">
         <v>187</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G34" s="31"/>
       <c r="H34" s="31" t="s">
@@ -6472,19 +6478,19 @@
         <v>56</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C35" s="31" t="s">
         <v>188</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="G35" s="31"/>
       <c r="H35" s="31" t="s">
@@ -6497,19 +6503,19 @@
         <v>56</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C36" s="31" t="s">
         <v>189</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G36" s="31"/>
       <c r="H36" s="31" t="s">
@@ -6522,19 +6528,19 @@
         <v>56</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C37" s="31" t="s">
         <v>163</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="G37" s="31"/>
       <c r="H37" s="31" t="s">
@@ -6547,23 +6553,23 @@
         <v>56</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C38" s="31" t="s">
         <v>190</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G38" s="31"/>
       <c r="H38" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I38" s="31"/>
     </row>
@@ -6572,26 +6578,26 @@
         <v>58</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C39" s="31" t="s">
         <v>218</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G39" s="31"/>
       <c r="H39" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I39" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -6599,26 +6605,26 @@
         <v>58</v>
       </c>
       <c r="B40" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C40" s="31" t="s">
         <v>162</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G40" s="31"/>
       <c r="H40" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I40" s="31" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -6626,19 +6632,19 @@
         <v>58</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C41" s="31" t="s">
         <v>219</v>
       </c>
       <c r="D41" s="31" t="s">
+        <v>500</v>
+      </c>
+      <c r="E41" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="E41" s="31" t="s">
-        <v>496</v>
-      </c>
       <c r="F41" s="31" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="G41" s="31"/>
       <c r="H41" s="31" t="s">
@@ -6651,19 +6657,19 @@
         <v>58</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C42" s="31" t="s">
         <v>220</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="G42" s="31"/>
       <c r="H42" s="31" t="s">
@@ -6676,19 +6682,19 @@
         <v>58</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C43" s="31" t="s">
         <v>221</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G43" s="31"/>
       <c r="H43" s="31" t="s">
@@ -6701,19 +6707,19 @@
         <v>58</v>
       </c>
       <c r="B44" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C44" s="31" t="s">
         <v>222</v>
       </c>
       <c r="D44" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G44" s="31"/>
       <c r="H44" s="31" t="s">
@@ -6726,19 +6732,19 @@
         <v>58</v>
       </c>
       <c r="B45" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C45" s="31" t="s">
         <v>223</v>
       </c>
       <c r="D45" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G45" s="31"/>
       <c r="H45" s="31" t="s">
@@ -6751,19 +6757,19 @@
         <v>58</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C46" s="31" t="s">
         <v>224</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G46" s="31"/>
       <c r="H46" s="31" t="s">
@@ -6776,26 +6782,26 @@
         <v>58</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C47" s="31" t="s">
         <v>225</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="G47" s="31"/>
       <c r="H47" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I47" s="31" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
@@ -6803,26 +6809,26 @@
         <v>60</v>
       </c>
       <c r="B48" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C48" s="31" t="s">
         <v>252</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G48" s="31"/>
       <c r="H48" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I48" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
@@ -6830,19 +6836,19 @@
         <v>60</v>
       </c>
       <c r="B49" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C49" s="31" t="s">
         <v>253</v>
       </c>
       <c r="D49" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E49" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F49" s="31" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G49" s="31"/>
       <c r="H49" s="31" t="s">
@@ -6855,19 +6861,19 @@
         <v>60</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C50" s="31" t="s">
         <v>254</v>
       </c>
       <c r="D50" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E50" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F50" s="31" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="G50" s="31"/>
       <c r="H50" s="31" t="s">
@@ -6880,19 +6886,19 @@
         <v>60</v>
       </c>
       <c r="B51" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C51" s="31" t="s">
         <v>255</v>
       </c>
       <c r="D51" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E51" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F51" s="31" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G51" s="31"/>
       <c r="H51" s="31" t="s">
@@ -6905,19 +6911,19 @@
         <v>60</v>
       </c>
       <c r="B52" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C52" s="31" t="s">
         <v>256</v>
       </c>
       <c r="D52" s="31" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E52" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F52" s="31" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G52" s="31"/>
       <c r="H52" s="31" t="s">
@@ -6930,19 +6936,19 @@
         <v>60</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C53" s="31" t="s">
         <v>257</v>
       </c>
       <c r="D53" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E53" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F53" s="31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G53" s="31"/>
       <c r="H53" s="31" t="s">
@@ -6955,26 +6961,26 @@
         <v>60</v>
       </c>
       <c r="B54" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C54" s="31" t="s">
         <v>258</v>
       </c>
       <c r="D54" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E54" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="G54" s="31"/>
       <c r="H54" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I54" s="31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
@@ -6982,19 +6988,19 @@
         <v>60</v>
       </c>
       <c r="B55" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C55" s="31" t="s">
         <v>259</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E55" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F55" s="31" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="G55" s="31"/>
       <c r="H55" s="31" t="s">
@@ -7007,19 +7013,19 @@
         <v>60</v>
       </c>
       <c r="B56" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C56" s="31" t="s">
         <v>260</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E56" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F56" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G56" s="31"/>
       <c r="H56" s="31" t="s">
@@ -7032,19 +7038,19 @@
         <v>60</v>
       </c>
       <c r="B57" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C57" s="31" t="s">
         <v>261</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E57" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F57" s="31" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="G57" s="31"/>
       <c r="H57" s="31" t="s">
@@ -7057,19 +7063,19 @@
         <v>60</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C58" s="31" t="s">
         <v>262</v>
       </c>
       <c r="D58" s="31" t="s">
+        <v>500</v>
+      </c>
+      <c r="E58" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="E58" s="31" t="s">
-        <v>496</v>
-      </c>
       <c r="F58" s="31" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G58" s="31"/>
       <c r="H58" s="31" t="s">
@@ -7082,19 +7088,19 @@
         <v>60</v>
       </c>
       <c r="B59" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C59" s="31" t="s">
         <v>263</v>
       </c>
       <c r="D59" s="31" t="s">
+        <v>500</v>
+      </c>
+      <c r="E59" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="E59" s="31" t="s">
-        <v>496</v>
-      </c>
       <c r="F59" s="31" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G59" s="31"/>
       <c r="H59" s="31" t="s">
@@ -7107,19 +7113,19 @@
         <v>60</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C60" s="31" t="s">
         <v>264</v>
       </c>
       <c r="D60" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E60" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F60" s="31" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G60" s="31"/>
       <c r="H60" s="31" t="s">
@@ -7132,19 +7138,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C61" s="31" t="s">
         <v>265</v>
       </c>
       <c r="D61" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E61" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F61" s="31" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="G61" s="31"/>
       <c r="H61" s="31" t="s">
@@ -7157,19 +7163,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C62" s="31" t="s">
         <v>266</v>
       </c>
       <c r="D62" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E62" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G62" s="31"/>
       <c r="H62" s="31" t="s">
@@ -7182,19 +7188,19 @@
         <v>60</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C63" s="31" t="s">
         <v>135</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E63" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F63" s="31" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G63" s="31"/>
       <c r="H63" s="31" t="s">
@@ -7207,19 +7213,19 @@
         <v>60</v>
       </c>
       <c r="B64" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C64" s="31" t="s">
         <v>267</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E64" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F64" s="31" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G64" s="31"/>
       <c r="H64" s="31" t="s">
@@ -7232,19 +7238,19 @@
         <v>60</v>
       </c>
       <c r="B65" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C65" s="31" t="s">
         <v>268</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E65" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F65" s="31" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G65" s="31"/>
       <c r="H65" s="31" t="s">
@@ -7257,19 +7263,19 @@
         <v>60</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C66" s="31" t="s">
         <v>269</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E66" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F66" s="31" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G66" s="31"/>
       <c r="H66" s="31" t="s">
@@ -7282,26 +7288,26 @@
         <v>62</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C67" s="31" t="s">
         <v>161</v>
       </c>
       <c r="D67" s="31" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E67" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F67" s="31" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G67" s="31"/>
       <c r="H67" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I67" s="31" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
@@ -7309,26 +7315,26 @@
         <v>62</v>
       </c>
       <c r="B68" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C68" s="31" t="s">
         <v>252</v>
       </c>
       <c r="D68" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E68" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G68" s="31"/>
       <c r="H68" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I68" s="31" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
@@ -7336,19 +7342,19 @@
         <v>62</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C69" s="31" t="s">
         <v>253</v>
       </c>
       <c r="D69" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E69" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F69" s="31" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G69" s="31"/>
       <c r="H69" s="31" t="s">
@@ -7361,19 +7367,19 @@
         <v>62</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C70" s="31" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D70" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E70" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F70" s="31" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G70" s="31"/>
       <c r="H70" s="31" t="s">
@@ -7386,19 +7392,19 @@
         <v>62</v>
       </c>
       <c r="B71" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C71" s="31" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D71" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E71" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F71" s="31" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G71" s="31"/>
       <c r="H71" s="31" t="s">
@@ -7411,19 +7417,19 @@
         <v>62</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C72" s="31" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D72" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E72" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F72" s="31" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G72" s="31"/>
       <c r="H72" s="31" t="s">
@@ -7436,19 +7442,19 @@
         <v>62</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C73" s="31" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D73" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E73" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F73" s="31" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G73" s="31"/>
       <c r="H73" s="31" t="s">
@@ -7461,19 +7467,19 @@
         <v>62</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C74" s="31" t="s">
         <v>268</v>
       </c>
       <c r="D74" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E74" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F74" s="31" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="G74" s="31"/>
       <c r="H74" s="31" t="s">
@@ -7486,26 +7492,26 @@
         <v>64</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C75" s="31" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D75" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E75" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F75" s="31" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G75" s="31"/>
       <c r="H75" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
@@ -7513,19 +7519,19 @@
         <v>64</v>
       </c>
       <c r="B76" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C76" s="31" t="s">
         <v>104</v>
       </c>
       <c r="D76" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E76" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F76" s="31" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G76" s="31"/>
       <c r="H76" s="31" t="s">
@@ -7538,19 +7544,19 @@
         <v>64</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C77" s="31" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D77" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E77" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F77" s="31" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G77" s="31"/>
       <c r="H77" s="31" t="s">
@@ -7563,22 +7569,22 @@
         <v>64</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C78" s="31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D78" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E78" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F78" s="31" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="G78" s="31" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H78" s="31" t="s">
         <v>142</v>
@@ -7590,19 +7596,19 @@
         <v>64</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C79" s="31" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D79" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E79" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F79" s="31" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="G79" s="31"/>
       <c r="H79" s="31" t="s">
@@ -7615,19 +7621,19 @@
         <v>64</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C80" s="31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D80" s="31" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E80" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F80" s="31" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G80" s="31"/>
       <c r="H80" s="31" t="s">
@@ -7640,19 +7646,19 @@
         <v>64</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C81" s="31" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D81" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E81" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F81" s="31" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G81" s="31"/>
       <c r="H81" s="31" t="s">
@@ -7665,19 +7671,19 @@
         <v>64</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C82" s="31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D82" s="31" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E82" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F82" s="31" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G82" s="31"/>
       <c r="H82" s="31" t="s">
@@ -7690,19 +7696,19 @@
         <v>64</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C83" s="31" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D83" s="31" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E83" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F83" s="31" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="G83" s="31"/>
       <c r="H83" s="31" t="s">
@@ -7715,19 +7721,19 @@
         <v>64</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C84" s="31" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D84" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E84" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F84" s="31" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G84" s="31"/>
       <c r="H84" s="31" t="s">
@@ -7740,19 +7746,19 @@
         <v>64</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C85" s="31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D85" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E85" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F85" s="31" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G85" s="31"/>
       <c r="H85" s="31" t="s">
@@ -7765,22 +7771,22 @@
         <v>64</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C86" s="31" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D86" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E86" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F86" s="31" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G86" s="31" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H86" s="31" t="s">
         <v>142</v>
@@ -7792,19 +7798,19 @@
         <v>64</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C87" s="31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D87" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E87" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F87" s="31" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G87" s="31"/>
       <c r="H87" s="31" t="s">
@@ -7817,19 +7823,19 @@
         <v>64</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C88" s="31" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D88" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E88" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F88" s="31" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G88" s="31"/>
       <c r="H88" s="31" t="s">
@@ -7842,19 +7848,19 @@
         <v>64</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C89" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D89" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E89" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F89" s="31" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G89" s="31"/>
       <c r="H89" s="31" t="s">
@@ -7867,26 +7873,26 @@
         <v>64</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C90" s="31" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D90" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E90" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F90" s="31" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G90" s="31"/>
       <c r="H90" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I90" s="31" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
@@ -7894,22 +7900,22 @@
         <v>64</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C91" s="31" t="s">
         <v>14</v>
       </c>
       <c r="D91" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E91" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F91" s="31" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G91" s="31" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H91" s="31" t="s">
         <v>142</v>
@@ -7921,23 +7927,23 @@
         <v>64</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C92" s="31" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D92" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E92" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F92" s="31" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G92" s="31"/>
       <c r="H92" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I92" s="31"/>
     </row>
@@ -7946,19 +7952,19 @@
         <v>64</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C93" s="31" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D93" s="31" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E93" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F93" s="31" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="G93" s="31"/>
       <c r="H93" s="31" t="s">
@@ -7971,19 +7977,19 @@
         <v>64</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C94" s="31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D94" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E94" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F94" s="31" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G94" s="31"/>
       <c r="H94" s="31" t="s">
@@ -7996,26 +8002,26 @@
         <v>66</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C95" s="31" t="s">
         <v>162</v>
       </c>
       <c r="D95" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E95" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F95" s="31" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G95" s="31"/>
       <c r="H95" s="31" t="s">
         <v>142</v>
       </c>
       <c r="I95" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
@@ -8023,19 +8029,19 @@
         <v>66</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C96" s="31" t="s">
         <v>135</v>
       </c>
       <c r="D96" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E96" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F96" s="31" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G96" s="31"/>
       <c r="H96" s="31" t="s">
@@ -8048,19 +8054,19 @@
         <v>66</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C97" s="31" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D97" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E97" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F97" s="31" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="G97" s="31"/>
       <c r="H97" s="31" t="s">
@@ -8073,19 +8079,19 @@
         <v>66</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C98" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D98" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E98" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F98" s="31" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G98" s="31"/>
       <c r="H98" s="31" t="s">
@@ -8098,19 +8104,19 @@
         <v>66</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C99" s="31" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D99" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F99" s="31" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G99" s="31"/>
       <c r="H99" s="31" t="s">
@@ -8123,19 +8129,19 @@
         <v>66</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D100" s="31" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E100" s="31" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F100" s="31" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G100" s="31"/>
       <c r="H100" s="31" t="s">
@@ -8148,19 +8154,19 @@
         <v>66</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C101" s="31" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D101" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E101" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F101" s="31" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G101" s="31"/>
       <c r="H101" s="31" t="s">
@@ -13357,7 +13363,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -13476,11 +13482,11 @@
         <v>0.6</v>
       </c>
       <c r="K5" s="21">
-        <f t="shared" ref="K5:K26" si="0">IF(A5="","",I5/H5)</f>
+        <f t="shared" ref="K5:K27" si="0">IF(A5="","",I5/H5)</f>
         <v>0.30695443645083931</v>
       </c>
       <c r="L5" s="21">
-        <f t="shared" ref="L5:L26" si="1">IF(A5="","",H5/AVERAGEIFS($H$5:$H$26,$B$5:$B$26,B5)-1)</f>
+        <f t="shared" ref="L5:L27" si="1">IF(A5="","",H5/AVERAGEIFS($H$5:$H$27,$B$5:$B$27,B5)-1)</f>
         <v>-0.21734234234234218</v>
       </c>
       <c r="M5" s="13">
@@ -13492,7 +13498,7 @@
         <v>860.5</v>
       </c>
       <c r="O5" s="13">
-        <f t="shared" ref="O5:O26" si="2">IF(A5="","",I5*N5)</f>
+        <f t="shared" ref="O5:O27" si="2">IF(A5="","",I5*N5)</f>
         <v>11014.400000000001</v>
       </c>
       <c r="P5" s="13">
@@ -13504,11 +13510,11 @@
         <v>3879448</v>
       </c>
       <c r="R5" s="15">
-        <f t="shared" ref="R5:R26" si="3">IF(OR(A5="",Q5=0),"",P5/Q5*1000)</f>
+        <f t="shared" ref="R5:R27" si="3">IF(OR(A5="",Q5=0),"",P5/Q5*1000)</f>
         <v>67.694166798987908</v>
       </c>
       <c r="S5" s="19" t="str">
-        <f t="shared" ref="S5:S26" si="4">IF(A5="","",IF(AND(L5&gt;0.15,K5&gt;0.5),"Alta",IF(OR(L5&gt;0.15,K5&gt;0.5),"Média","Baixa")))</f>
+        <f t="shared" ref="S5:S27" si="4">IF(A5="","",IF(AND(L5&gt;0.15,K5&gt;0.5),"Alta",IF(OR(L5&gt;0.15,K5&gt;0.5),"Média","Baixa")))</f>
         <v>Baixa</v>
       </c>
     </row>
@@ -14161,7 +14167,7 @@
       </c>
       <c r="L15" s="21">
         <f t="shared" si="1"/>
-        <v>-0.27524523946912871</v>
+        <v>-0.25592417061611383</v>
       </c>
       <c r="M15" s="13">
         <f>IF(A15="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A15,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
@@ -14229,7 +14235,7 @@
       </c>
       <c r="L16" s="21">
         <f t="shared" si="1"/>
-        <v>0.43796884016156934</v>
+        <v>0.47630331753554489</v>
       </c>
       <c r="M16" s="13">
         <f>IF(A16="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A16,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
@@ -14297,7 +14303,7 @@
       </c>
       <c r="L17" s="21">
         <f t="shared" si="1"/>
-        <v>-9.8095787651472088E-3</v>
+        <v>1.6587677725118377E-2</v>
       </c>
       <c r="M17" s="13">
         <f>IF(A17="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A17,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
@@ -14365,7 +14371,7 @@
       </c>
       <c r="L18" s="21">
         <f t="shared" si="1"/>
-        <v>0.43566070398153478</v>
+        <v>0.47393364928909953</v>
       </c>
       <c r="M18" s="13">
         <f>IF(A18="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A18,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
@@ -14433,7 +14439,7 @@
       </c>
       <c r="L19" s="21">
         <f t="shared" si="1"/>
-        <v>-4.6739757645701263E-2</v>
+        <v>-2.1327014218009643E-2</v>
       </c>
       <c r="M19" s="13">
         <f>IF(A19="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A19,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
@@ -14501,7 +14507,7 @@
       </c>
       <c r="L20" s="21">
         <f t="shared" si="1"/>
-        <v>-1.2117714945181879E-2</v>
+        <v>1.42180094786728E-2</v>
       </c>
       <c r="M20" s="13">
         <f>IF(A20="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A20,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
@@ -14569,7 +14575,7 @@
       </c>
       <c r="L21" s="21">
         <f t="shared" si="1"/>
-        <v>-0.24062319676860944</v>
+        <v>-0.22037914691943139</v>
       </c>
       <c r="M21" s="13">
         <f>IF(A21="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A21,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
@@ -14637,7 +14643,7 @@
       </c>
       <c r="L22" s="21">
         <f t="shared" si="1"/>
-        <v>-0.2890940565493364</v>
+        <v>-0.27014218009478674</v>
       </c>
       <c r="M22" s="13">
         <f>IF(A22="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A22,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
@@ -14673,10 +14679,10 @@
         <v>295</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C23" s="20">
-        <v>2013</v>
+        <v>2026</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>296</v>
@@ -14691,45 +14697,45 @@
         <v>272</v>
       </c>
       <c r="H23" s="12">
-        <v>18.5</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="I23" s="12">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J23" s="12">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="K23" s="21">
         <f t="shared" si="0"/>
-        <v>0.35675675675675672</v>
+        <v>0.22289156626506024</v>
       </c>
       <c r="L23" s="21">
         <f t="shared" si="1"/>
-        <v>3.0640668523676862E-2</v>
+        <v>-0.21327014218009477</v>
       </c>
       <c r="M23" s="13">
         <f>IF(A23="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A23,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>4846.0999999999995</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13">
         <f>IF(A23="","",SUMIFS(tbl_energia_maquina[Horas_Paragem],tbl_energia_maquina[ID_Maquina],A23,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>896.10000000000014</v>
+        <v>0</v>
       </c>
       <c r="O23" s="13">
         <f t="shared" si="2"/>
-        <v>5914.26</v>
+        <v>0</v>
       </c>
       <c r="P23" s="13">
         <f>IF(A23="","",SUMIFS(tbl_energia_maquina[kWh_Rateado],tbl_energia_maquina[ID_Maquina],A23,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>91469</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="13">
         <f>IF(A23="","",SUMIFS(tbl_energia_maquina[Unid],tbl_energia_maquina[ID_Maquina],A23,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>2408373</v>
-      </c>
-      <c r="R23" s="15">
+        <v>0</v>
+      </c>
+      <c r="R23" s="15" t="str">
         <f t="shared" si="3"/>
-        <v>37.979582066399182</v>
+        <v/>
       </c>
       <c r="S23" s="19" t="str">
         <f t="shared" si="4"/>
@@ -14747,7 +14753,7 @@
         <v>2013</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E24" s="16">
         <v>46193</v>
@@ -14759,45 +14765,45 @@
         <v>272</v>
       </c>
       <c r="H24" s="12">
-        <v>17.399999999999999</v>
+        <v>17.7</v>
       </c>
       <c r="I24" s="12">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J24" s="12">
         <v>0.2</v>
       </c>
       <c r="K24" s="21">
         <f t="shared" si="0"/>
-        <v>0.36206896551724138</v>
+        <v>0.36158192090395486</v>
       </c>
       <c r="L24" s="21">
         <f t="shared" si="1"/>
-        <v>-3.0640668523676973E-2</v>
+        <v>-1.6666666666666718E-2</v>
       </c>
       <c r="M24" s="13">
         <f>IF(A24="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A24,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>4160.8999999999996</v>
+        <v>4846.0999999999995</v>
       </c>
       <c r="N24" s="13">
         <f>IF(A24="","",SUMIFS(tbl_energia_maquina[Horas_Paragem],tbl_energia_maquina[ID_Maquina],A24,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>580.89999999999986</v>
+        <v>896.10000000000014</v>
       </c>
       <c r="O24" s="13">
         <f t="shared" si="2"/>
-        <v>3659.6699999999992</v>
+        <v>5735.0400000000009</v>
       </c>
       <c r="P24" s="13">
         <f>IF(A24="","",SUMIFS(tbl_energia_maquina[kWh_Rateado],tbl_energia_maquina[ID_Maquina],A24,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>72296</v>
+        <v>87878</v>
       </c>
       <c r="Q24" s="13">
         <f>IF(A24="","",SUMIFS(tbl_energia_maquina[Unid],tbl_energia_maquina[ID_Maquina],A24,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>2116976</v>
+        <v>2408373</v>
       </c>
       <c r="R24" s="15">
         <f t="shared" si="3"/>
-        <v>34.15059972337901</v>
+        <v>36.488533960478712</v>
       </c>
       <c r="S24" s="19" t="str">
         <f t="shared" si="4"/>
@@ -14806,16 +14812,16 @@
     </row>
     <row r="25" spans="1:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="20">
+        <v>2013</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>298</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C25" s="20">
-        <v>2023</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>299</v>
       </c>
       <c r="E25" s="16">
         <v>46193</v>
@@ -14827,49 +14833,49 @@
         <v>272</v>
       </c>
       <c r="H25" s="12">
-        <v>9</v>
+        <v>18.3</v>
       </c>
       <c r="I25" s="12">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="J25" s="12">
         <v>0.2</v>
       </c>
       <c r="K25" s="21">
         <f t="shared" si="0"/>
-        <v>0.55555555555555558</v>
+        <v>0.34972677595628415</v>
       </c>
       <c r="L25" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.6666666666666607E-2</v>
       </c>
       <c r="M25" s="13">
         <f>IF(A25="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A25,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>6777.5000000000009</v>
+        <v>4160.8999999999996</v>
       </c>
       <c r="N25" s="13">
         <f>IF(A25="","",SUMIFS(tbl_energia_maquina[Horas_Paragem],tbl_energia_maquina[ID_Maquina],A25,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>938.5</v>
+        <v>580.89999999999986</v>
       </c>
       <c r="O25" s="13">
         <f t="shared" si="2"/>
-        <v>4692.5</v>
+        <v>3717.7599999999993</v>
       </c>
       <c r="P25" s="13">
         <f>IF(A25="","",SUMIFS(tbl_energia_maquina[kWh_Rateado],tbl_energia_maquina[ID_Maquina],A25,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>61482</v>
+        <v>75887</v>
       </c>
       <c r="Q25" s="13">
         <f>IF(A25="","",SUMIFS(tbl_energia_maquina[Unid],tbl_energia_maquina[ID_Maquina],A25,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>3163985</v>
+        <v>2116976</v>
       </c>
       <c r="R25" s="15">
         <f t="shared" si="3"/>
-        <v>19.431824107889259</v>
+        <v>35.846887258051112</v>
       </c>
       <c r="S25" s="19" t="str">
         <f t="shared" si="4"/>
-        <v>Média</v>
+        <v>Baixa</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14880,10 +14886,10 @@
         <v>172</v>
       </c>
       <c r="C26" s="20">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E26" s="16">
         <v>46195</v>
@@ -14895,53 +14901,121 @@
         <v>272</v>
       </c>
       <c r="H26" s="12">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I26" s="12">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="J26" s="12">
         <v>0.2</v>
       </c>
       <c r="K26" s="21">
         <f t="shared" si="0"/>
-        <v>0.51111111111111107</v>
+        <v>0.5056179775280899</v>
       </c>
       <c r="L26" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1.1111111111111072E-2</v>
       </c>
       <c r="M26" s="13">
         <f>IF(A26="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A26,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>6511.9</v>
+        <v>6777.5000000000009</v>
       </c>
       <c r="N26" s="13">
         <f>IF(A26="","",SUMIFS(tbl_energia_maquina[Horas_Paragem],tbl_energia_maquina[ID_Maquina],A26,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>883.29999999999984</v>
+        <v>938.5</v>
       </c>
       <c r="O26" s="13">
         <f t="shared" si="2"/>
-        <v>4063.1799999999989</v>
+        <v>4223.25</v>
       </c>
       <c r="P26" s="13">
         <f>IF(A26="","",SUMIFS(tbl_energia_maquina[kWh_Rateado],tbl_energia_maquina[ID_Maquina],A26,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>58585</v>
+        <v>60452</v>
       </c>
       <c r="Q26" s="13">
         <f>IF(A26="","",SUMIFS(tbl_energia_maquina[Unid],tbl_energia_maquina[ID_Maquina],A26,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
-        <v>3071363</v>
+        <v>3163985</v>
       </c>
       <c r="R26" s="15">
         <f t="shared" si="3"/>
-        <v>19.074593266898116</v>
+        <v>19.106285269999699</v>
       </c>
       <c r="S26" s="19" t="str">
         <f t="shared" si="4"/>
         <v>Média</v>
       </c>
     </row>
+    <row r="27" spans="1:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" s="20">
+        <v>2021</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E27" s="16">
+        <v>46195</v>
+      </c>
+      <c r="F27" s="20">
+        <v>48</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="H27" s="12">
+        <v>9.1</v>
+      </c>
+      <c r="I27" s="12">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="J27" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="K27" s="21">
+        <f t="shared" si="0"/>
+        <v>0.56043956043956045</v>
+      </c>
+      <c r="L27" s="21">
+        <f t="shared" si="1"/>
+        <v>1.1111111111111072E-2</v>
+      </c>
+      <c r="M27" s="13">
+        <f>IF(A27="","",SUMIFS(tbl_energia_maquina[Horas_Marcha],tbl_energia_maquina[ID_Maquina],A27,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
+        <v>6511.9</v>
+      </c>
+      <c r="N27" s="13">
+        <f>IF(A27="","",SUMIFS(tbl_energia_maquina[Horas_Paragem],tbl_energia_maquina[ID_Maquina],A27,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
+        <v>883.29999999999984</v>
+      </c>
+      <c r="O27" s="13">
+        <f t="shared" si="2"/>
+        <v>4504.829999999999</v>
+      </c>
+      <c r="P27" s="13">
+        <f>IF(A27="","",SUMIFS(tbl_energia_maquina[kWh_Rateado],tbl_energia_maquina[ID_Maquina],A27,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
+        <v>59613</v>
+      </c>
+      <c r="Q27" s="13">
+        <f>IF(A27="","",SUMIFS(tbl_energia_maquina[Unid],tbl_energia_maquina[ID_Maquina],A27,tbl_energia_maquina[Mes],"&gt;="&amp;DATE(2026,1,1)))</f>
+        <v>3071363</v>
+      </c>
+      <c r="R27" s="15">
+        <f t="shared" si="3"/>
+        <v>19.409298086875435</v>
+      </c>
+      <c r="S27" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>Média</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="S5:S226">
+  <conditionalFormatting sqref="S5:S227">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>ISNUMBER(SEARCH("Alta",S5))</formula>
     </cfRule>
@@ -14980,12 +15054,12 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
@@ -14999,16 +15073,16 @@
         <v>253</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>268</v>
@@ -15019,7 +15093,7 @@
         <v>45839</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>172</v>
@@ -15034,11 +15108,11 @@
         <v>97</v>
       </c>
       <c r="G5" s="17">
-        <v>9046</v>
+        <v>8961</v>
       </c>
       <c r="H5" s="15">
         <f t="shared" ref="H5:H68" si="0">IF(OR(A5="",D5=0),"",G5/D5*1000)</f>
-        <v>19.706429533066981</v>
+        <v>19.521259677848018</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15046,7 +15120,7 @@
         <v>45839</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>172</v>
@@ -15061,11 +15135,11 @@
         <v>49.2</v>
       </c>
       <c r="G6" s="17">
-        <v>3538</v>
+        <v>3623</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="0"/>
-        <v>20.208366652196759</v>
+        <v>20.693870090703467</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15451,7 +15525,7 @@
         <v>45839</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>171</v>
@@ -15466,11 +15540,11 @@
         <v>65.900000000000006</v>
       </c>
       <c r="G21" s="17">
-        <v>8921</v>
+        <v>8557</v>
       </c>
       <c r="H21" s="15">
         <f t="shared" si="0"/>
-        <v>36.942253142017101</v>
+        <v>35.434913141602998</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15478,7 +15552,7 @@
         <v>45839</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>171</v>
@@ -15493,11 +15567,11 @@
         <v>61.8</v>
       </c>
       <c r="G22" s="17">
-        <v>7021</v>
+        <v>7385</v>
       </c>
       <c r="H22" s="15">
         <f t="shared" si="0"/>
-        <v>34.758286096190503</v>
+        <v>36.560310898784621</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15505,7 +15579,7 @@
         <v>45870</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>172</v>
@@ -15520,11 +15594,11 @@
         <v>88.4</v>
       </c>
       <c r="G23" s="17">
-        <v>6978</v>
+        <v>6866</v>
       </c>
       <c r="H23" s="15">
         <f t="shared" si="0"/>
-        <v>19.494560632050646</v>
+        <v>19.181664273382019</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15532,7 +15606,7 @@
         <v>45870</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>172</v>
@@ -15547,11 +15621,11 @@
         <v>94.5</v>
       </c>
       <c r="G24" s="17">
-        <v>6232</v>
+        <v>6344</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="0"/>
-        <v>19.243298657106774</v>
+        <v>19.58913457648995</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15937,7 +16011,7 @@
         <v>45870</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>171</v>
@@ -15952,11 +16026,11 @@
         <v>46.5</v>
       </c>
       <c r="G39" s="17">
-        <v>3132</v>
+        <v>2956</v>
       </c>
       <c r="H39" s="15">
         <f t="shared" si="0"/>
-        <v>38.58425831249307</v>
+        <v>36.41604967168886</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15964,7 +16038,7 @@
         <v>45870</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>171</v>
@@ -15979,11 +16053,11 @@
         <v>39.1</v>
       </c>
       <c r="G40" s="17">
-        <v>5123</v>
+        <v>5299</v>
       </c>
       <c r="H40" s="15">
         <f t="shared" si="0"/>
-        <v>32.716636757840689</v>
+        <v>33.840612566815892</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15991,7 +16065,7 @@
         <v>45901</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>172</v>
@@ -16006,11 +16080,11 @@
         <v>70.400000000000006</v>
       </c>
       <c r="G41" s="17">
-        <v>5717</v>
+        <v>5625</v>
       </c>
       <c r="H41" s="15">
         <f t="shared" si="0"/>
-        <v>19.500631033188935</v>
+        <v>19.18681993382679</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16018,7 +16092,7 @@
         <v>45901</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>172</v>
@@ -16033,11 +16107,11 @@
         <v>67.3</v>
       </c>
       <c r="G42" s="17">
-        <v>5419</v>
+        <v>5510</v>
       </c>
       <c r="H42" s="15">
         <f t="shared" si="0"/>
-        <v>19.402354491292392</v>
+        <v>19.728173693858842</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16423,7 +16497,7 @@
         <v>45901</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>171</v>
@@ -16438,11 +16512,11 @@
         <v>46</v>
       </c>
       <c r="G57" s="17">
-        <v>4244</v>
+        <v>3995</v>
       </c>
       <c r="H57" s="15">
         <f t="shared" si="0"/>
-        <v>34.980136162075731</v>
+        <v>32.927814318447815</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16450,7 +16524,7 @@
         <v>45901</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>171</v>
@@ -16465,11 +16539,11 @@
         <v>61.1</v>
       </c>
       <c r="G58" s="17">
-        <v>7719</v>
+        <v>7968</v>
       </c>
       <c r="H58" s="15">
         <f t="shared" si="0"/>
-        <v>30.75715435557008</v>
+        <v>31.749320625104598</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16477,7 +16551,7 @@
         <v>45931</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>172</v>
@@ -16492,11 +16566,11 @@
         <v>85.4</v>
       </c>
       <c r="G59" s="17">
-        <v>5007</v>
+        <v>4918</v>
       </c>
       <c r="H59" s="15">
         <f t="shared" si="0"/>
-        <v>18.696299947350141</v>
+        <v>18.363971068717397</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16504,7 +16578,7 @@
         <v>45931</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>172</v>
@@ -16519,11 +16593,11 @@
         <v>72.7</v>
       </c>
       <c r="G60" s="17">
-        <v>5164</v>
+        <v>5253</v>
       </c>
       <c r="H60" s="15">
         <f t="shared" si="0"/>
-        <v>18.265421618562534</v>
+        <v>18.580220713073004</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16909,7 +16983,7 @@
         <v>45931</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C75" s="9" t="s">
         <v>171</v>
@@ -16924,11 +16998,11 @@
         <v>102.6</v>
       </c>
       <c r="G75" s="17">
-        <v>9169</v>
+        <v>8826</v>
       </c>
       <c r="H75" s="15">
         <f t="shared" si="1"/>
-        <v>36.906592389248026</v>
+        <v>35.525966237049083</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16936,7 +17010,7 @@
         <v>45931</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C76" s="9" t="s">
         <v>171</v>
@@ -16951,11 +17025,11 @@
         <v>64.400000000000006</v>
       </c>
       <c r="G76" s="17">
-        <v>6239</v>
+        <v>6582</v>
       </c>
       <c r="H76" s="15">
         <f t="shared" si="1"/>
-        <v>34.092523578977286</v>
+        <v>35.966820034753717</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16963,7 +17037,7 @@
         <v>45962</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C77" s="9" t="s">
         <v>172</v>
@@ -16978,11 +17052,11 @@
         <v>90.1</v>
       </c>
       <c r="G77" s="17">
-        <v>5228</v>
+        <v>5137</v>
       </c>
       <c r="H77" s="15">
         <f t="shared" si="1"/>
-        <v>19.435305488949609</v>
+        <v>19.097009238089928</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -16990,7 +17064,7 @@
         <v>45962</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>172</v>
@@ -17005,11 +17079,11 @@
         <v>67.400000000000006</v>
       </c>
       <c r="G78" s="17">
-        <v>5266</v>
+        <v>5357</v>
       </c>
       <c r="H78" s="15">
         <f t="shared" si="1"/>
-        <v>18.863193489225125</v>
+        <v>19.189162081613937</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17395,7 +17469,7 @@
         <v>45962</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C93" s="9" t="s">
         <v>171</v>
@@ -17410,11 +17484,11 @@
         <v>76.7</v>
       </c>
       <c r="G93" s="17">
-        <v>6723</v>
+        <v>6363</v>
       </c>
       <c r="H93" s="15">
         <f t="shared" si="1"/>
-        <v>38.530091066956274</v>
+        <v>36.466900112902394</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17422,7 +17496,7 @@
         <v>45962</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C94" s="9" t="s">
         <v>171</v>
@@ -17437,11 +17511,11 @@
         <v>78.599999999999994</v>
       </c>
       <c r="G94" s="17">
-        <v>9540</v>
+        <v>9899</v>
       </c>
       <c r="H94" s="15">
         <f t="shared" si="1"/>
-        <v>34.81624758220503</v>
+        <v>36.126418743841469</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17449,7 +17523,7 @@
         <v>45992</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C95" s="9" t="s">
         <v>172</v>
@@ -17464,11 +17538,11 @@
         <v>66.400000000000006</v>
       </c>
       <c r="G95" s="17">
-        <v>5032</v>
+        <v>4940</v>
       </c>
       <c r="H95" s="15">
         <f t="shared" si="1"/>
-        <v>19.301435333287305</v>
+        <v>18.94854740589016</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17476,7 +17550,7 @@
         <v>45992</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C96" s="9" t="s">
         <v>172</v>
@@ -17491,11 +17565,11 @@
         <v>82.3</v>
       </c>
       <c r="G96" s="17">
-        <v>6130</v>
+        <v>6222</v>
       </c>
       <c r="H96" s="15">
         <f t="shared" si="1"/>
-        <v>19.679162239122686</v>
+        <v>19.974510187899082</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17881,7 +17955,7 @@
         <v>45992</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C111" s="9" t="s">
         <v>171</v>
@@ -17896,11 +17970,11 @@
         <v>157.5</v>
       </c>
       <c r="G111" s="17">
-        <v>7981</v>
+        <v>7716</v>
       </c>
       <c r="H111" s="15">
         <f t="shared" si="1"/>
-        <v>38.910448925465111</v>
+        <v>37.618471859276887</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17908,7 +17982,7 @@
         <v>45992</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C112" s="9" t="s">
         <v>171</v>
@@ -17923,11 +17997,11 @@
         <v>43.8</v>
       </c>
       <c r="G112" s="17">
-        <v>4485</v>
+        <v>4750</v>
       </c>
       <c r="H112" s="15">
         <f t="shared" si="1"/>
-        <v>33.552026213221822</v>
+        <v>35.534475922587212</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17935,7 +18009,7 @@
         <v>46023</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C113" s="9" t="s">
         <v>172</v>
@@ -17950,11 +18024,11 @@
         <v>67</v>
       </c>
       <c r="G113" s="17">
-        <v>3621</v>
+        <v>3540</v>
       </c>
       <c r="H113" s="15">
         <f t="shared" si="1"/>
-        <v>19.320552564601929</v>
+        <v>18.88836124791241</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17962,7 +18036,7 @@
         <v>46023</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C114" s="9" t="s">
         <v>172</v>
@@ -17977,11 +18051,11 @@
         <v>105.6</v>
       </c>
       <c r="G114" s="17">
-        <v>5348</v>
+        <v>5429</v>
       </c>
       <c r="H114" s="15">
         <f t="shared" si="1"/>
-        <v>18.974901187173138</v>
+        <v>19.262292173740271</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18367,7 +18441,7 @@
         <v>46023</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C129" s="9" t="s">
         <v>171</v>
@@ -18382,11 +18456,11 @@
         <v>68.099999999999994</v>
       </c>
       <c r="G129" s="17">
-        <v>5913</v>
+        <v>5681</v>
       </c>
       <c r="H129" s="15">
         <f t="shared" si="1"/>
-        <v>36.802141034418376</v>
+        <v>35.358187589469097</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18394,7 +18468,7 @@
         <v>46023</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C130" s="9" t="s">
         <v>171</v>
@@ -18409,11 +18483,11 @@
         <v>32.299999999999997</v>
       </c>
       <c r="G130" s="17">
-        <v>4307</v>
+        <v>4539</v>
       </c>
       <c r="H130" s="15">
         <f t="shared" si="1"/>
-        <v>31.609385205897677</v>
+        <v>33.312050023118083</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18421,7 +18495,7 @@
         <v>46054</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C131" s="9" t="s">
         <v>172</v>
@@ -18436,11 +18510,11 @@
         <v>87.1</v>
       </c>
       <c r="G131" s="17">
-        <v>5551</v>
+        <v>5468</v>
       </c>
       <c r="H131" s="15">
         <f t="shared" si="1"/>
-        <v>19.163582633672117</v>
+        <v>18.877043747238179</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18448,7 +18522,7 @@
         <v>46054</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C132" s="9" t="s">
         <v>172</v>
@@ -18463,11 +18537,11 @@
         <v>54.2</v>
       </c>
       <c r="G132" s="17">
-        <v>4378</v>
+        <v>4461</v>
       </c>
       <c r="H132" s="15">
         <f t="shared" si="1"/>
-        <v>18.448054273855423</v>
+        <v>18.797800391884206</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18853,7 +18927,7 @@
         <v>46054</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C147" s="9" t="s">
         <v>171</v>
@@ -18868,11 +18942,11 @@
         <v>73.3</v>
       </c>
       <c r="G147" s="17">
-        <v>4930</v>
+        <v>4687</v>
       </c>
       <c r="H147" s="15">
         <f t="shared" si="2"/>
-        <v>39.162727886563133</v>
+        <v>37.232394645906979</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18880,7 +18954,7 @@
         <v>46054</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C148" s="9" t="s">
         <v>171</v>
@@ -18895,11 +18969,11 @@
         <v>36.4</v>
       </c>
       <c r="G148" s="17">
-        <v>5742</v>
+        <v>5985</v>
       </c>
       <c r="H148" s="15">
         <f t="shared" si="2"/>
-        <v>33.899505853598058</v>
+        <v>35.334124439878856</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18907,7 +18981,7 @@
         <v>46082</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C149" s="9" t="s">
         <v>172</v>
@@ -18922,11 +18996,11 @@
         <v>69.2</v>
       </c>
       <c r="G149" s="17">
-        <v>4988</v>
+        <v>4897</v>
       </c>
       <c r="H149" s="15">
         <f t="shared" si="2"/>
-        <v>19.35711707796013</v>
+        <v>19.003969994140085</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -18934,7 +19008,7 @@
         <v>46082</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C150" s="9" t="s">
         <v>172</v>
@@ -18949,11 +19023,11 @@
         <v>93.4</v>
       </c>
       <c r="G150" s="17">
-        <v>5491</v>
+        <v>5582</v>
       </c>
       <c r="H150" s="15">
         <f t="shared" si="2"/>
-        <v>19.229152950734704</v>
+        <v>19.547829497541638</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -19339,7 +19413,7 @@
         <v>46082</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C165" s="9" t="s">
         <v>171</v>
@@ -19354,11 +19428,11 @@
         <v>92.6</v>
       </c>
       <c r="G165" s="17">
-        <v>5660</v>
+        <v>5361</v>
       </c>
       <c r="H165" s="15">
         <f t="shared" si="2"/>
-        <v>39.276916137538599</v>
+        <v>37.202040179036118</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -19366,7 +19440,7 @@
         <v>46082</v>
       </c>
       <c r="B166" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C166" s="9" t="s">
         <v>171</v>
@@ -19381,11 +19455,11 @@
         <v>62.7</v>
       </c>
       <c r="G166" s="17">
-        <v>7836</v>
+        <v>8135</v>
       </c>
       <c r="H166" s="15">
         <f t="shared" si="2"/>
-        <v>33.187780323661329</v>
+        <v>34.454133860768877</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -19393,7 +19467,7 @@
         <v>46113</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C167" s="9" t="s">
         <v>172</v>
@@ -19408,11 +19482,11 @@
         <v>111.2</v>
       </c>
       <c r="G167" s="17">
-        <v>5256</v>
+        <v>5173</v>
       </c>
       <c r="H167" s="15">
         <f t="shared" si="2"/>
-        <v>19.737953877178555</v>
+        <v>19.42626244418658</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -19420,7 +19494,7 @@
         <v>46113</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C168" s="9" t="s">
         <v>172</v>
@@ -19435,11 +19509,11 @@
         <v>61.8</v>
       </c>
       <c r="G168" s="17">
-        <v>3711</v>
+        <v>3794</v>
       </c>
       <c r="H168" s="15">
         <f t="shared" si="2"/>
-        <v>18.748294920631711</v>
+        <v>19.167618143054895</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -19825,7 +19899,7 @@
         <v>46113</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C183" s="9" t="s">
         <v>171</v>
@@ -19840,11 +19914,11 @@
         <v>118.5</v>
       </c>
       <c r="G183" s="17">
-        <v>6986</v>
+        <v>6688</v>
       </c>
       <c r="H183" s="15">
         <f t="shared" si="2"/>
-        <v>40.282542885973761</v>
+        <v>38.56422084474557</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -19852,7 +19926,7 @@
         <v>46113</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C184" s="9" t="s">
         <v>171</v>
@@ -19867,11 +19941,11 @@
         <v>57.9</v>
       </c>
       <c r="G184" s="17">
-        <v>6101</v>
+        <v>6399</v>
       </c>
       <c r="H184" s="15">
         <f t="shared" si="2"/>
-        <v>32.405759843627997</v>
+        <v>33.988601416058934</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -19879,7 +19953,7 @@
         <v>46143</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C185" s="9" t="s">
         <v>172</v>
@@ -19894,11 +19968,11 @@
         <v>60.2</v>
       </c>
       <c r="G185" s="17">
-        <v>4673</v>
+        <v>4590</v>
       </c>
       <c r="H185" s="15">
         <f t="shared" si="2"/>
-        <v>18.522335407665782</v>
+        <v>18.193348923857464</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -19906,7 +19980,7 @@
         <v>46143</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C186" s="9" t="s">
         <v>172</v>
@@ -19921,11 +19995,11 @@
         <v>79.7</v>
       </c>
       <c r="G186" s="17">
-        <v>5236</v>
+        <v>5319</v>
       </c>
       <c r="H186" s="15">
         <f t="shared" si="2"/>
-        <v>18.911812297734627</v>
+        <v>19.211598474341191</v>
       </c>
     </row>
     <row r="187" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -20311,7 +20385,7 @@
         <v>46143</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C201" s="9" t="s">
         <v>171</v>
@@ -20326,11 +20400,11 @@
         <v>169.5</v>
       </c>
       <c r="G201" s="17">
-        <v>7877</v>
+        <v>7550</v>
       </c>
       <c r="H201" s="15">
         <f t="shared" si="3"/>
-        <v>40.806705623937994</v>
+        <v>39.112685979526709</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -20338,7 +20412,7 @@
         <v>46143</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C202" s="9" t="s">
         <v>171</v>
@@ -20353,11 +20427,11 @@
         <v>56.5</v>
       </c>
       <c r="G202" s="17">
-        <v>6534</v>
+        <v>6860</v>
       </c>
       <c r="H202" s="15">
         <f t="shared" si="3"/>
-        <v>32.845064192144129</v>
+        <v>34.483798646787378</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -20365,7 +20439,7 @@
         <v>46174</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C203" s="9" t="s">
         <v>172</v>
@@ -20380,11 +20454,11 @@
         <v>46.2</v>
       </c>
       <c r="G203" s="17">
-        <v>4188</v>
+        <v>4113</v>
       </c>
       <c r="H203" s="15">
         <f t="shared" si="3"/>
-        <v>18.629810365612251</v>
+        <v>18.29618195648596</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -20392,7 +20466,7 @@
         <v>46174</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C204" s="9" t="s">
         <v>172</v>
@@ -20407,11 +20481,11 @@
         <v>65.599999999999994</v>
       </c>
       <c r="G204" s="17">
-        <v>5277</v>
+        <v>5351</v>
       </c>
       <c r="H204" s="15">
         <f t="shared" si="3"/>
-        <v>18.558832942368088</v>
+        <v>18.819085668867093</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -20797,7 +20871,7 @@
         <v>46174</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C219" s="9" t="s">
         <v>171</v>
@@ -20812,11 +20886,11 @@
         <v>121.7</v>
       </c>
       <c r="G219" s="17">
-        <v>3666</v>
+        <v>3475</v>
       </c>
       <c r="H219" s="15">
         <f t="shared" si="3"/>
-        <v>40.782725745625257</v>
+        <v>38.657930159860278</v>
       </c>
     </row>
     <row r="220" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -20824,7 +20898,7 @@
         <v>46174</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C220" s="9" t="s">
         <v>171</v>
@@ -20839,11 +20913,11 @@
         <v>50</v>
       </c>
       <c r="G220" s="17">
-        <v>5058</v>
+        <v>5248</v>
       </c>
       <c r="H220" s="15">
         <f t="shared" si="3"/>
-        <v>30.781776798646529</v>
+        <v>31.938071300770456</v>
       </c>
     </row>
     <row r="221" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -20851,7 +20925,7 @@
         <v>46204</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C221" s="9" t="s">
         <v>172</v>
@@ -20866,11 +20940,11 @@
         <v>61.6</v>
       </c>
       <c r="G221" s="17">
-        <v>5292</v>
+        <v>5214</v>
       </c>
       <c r="H221" s="15">
         <f t="shared" si="3"/>
-        <v>19.495518462167567</v>
+        <v>19.20816955059367</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -20878,7 +20952,7 @@
         <v>46204</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C222" s="9" t="s">
         <v>172</v>
@@ -20893,11 +20967,11 @@
         <v>67.8</v>
       </c>
       <c r="G222" s="17">
-        <v>3903</v>
+        <v>3981</v>
       </c>
       <c r="H222" s="15">
         <f t="shared" si="3"/>
-        <v>20.001127401493292</v>
+        <v>20.400842476388625</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -21391,7 +21465,7 @@
         <v>46204</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C241" s="9" t="s">
         <v>171</v>
@@ -21406,11 +21480,11 @@
         <v>58.4</v>
       </c>
       <c r="G241" s="17">
-        <v>10707</v>
+        <v>10398</v>
       </c>
       <c r="H241" s="15">
         <f t="shared" si="3"/>
-        <v>35.965616507838405</v>
+        <v>34.92766231890387</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -21418,7 +21492,7 @@
         <v>46204</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C242" s="9" t="s">
         <v>171</v>
@@ -21433,11 +21507,11 @@
         <v>32.1</v>
       </c>
       <c r="G242" s="17">
-        <v>4719</v>
+        <v>5028</v>
       </c>
       <c r="H242" s="15">
         <f t="shared" si="3"/>
-        <v>33.729307830860279</v>
+        <v>35.937902049918513</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -21445,7 +21519,7 @@
         <v>46235</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C243" s="9" t="s">
         <v>172</v>
@@ -21460,11 +21534,11 @@
         <v>92.7</v>
       </c>
       <c r="G243" s="17">
-        <v>5268</v>
+        <v>5174</v>
       </c>
       <c r="H243" s="15">
         <f t="shared" si="3"/>
-        <v>20.044670545216562</v>
+        <v>19.687001784538815</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -21472,7 +21546,7 @@
         <v>46235</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C244" s="9" t="s">
         <v>172</v>
@@ -21487,11 +21561,11 @@
         <v>64.8</v>
       </c>
       <c r="G244" s="17">
-        <v>5595</v>
+        <v>5689</v>
       </c>
       <c r="H244" s="15">
         <f t="shared" si="3"/>
-        <v>19.063811808319247</v>
+        <v>19.384097475876356</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -21985,7 +22059,7 @@
         <v>46235</v>
       </c>
       <c r="B263" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C263" s="9" t="s">
         <v>171</v>
@@ -22000,11 +22074,11 @@
         <v>43.6</v>
       </c>
       <c r="G263" s="17">
-        <v>9517</v>
+        <v>9164</v>
       </c>
       <c r="H263" s="15">
         <f t="shared" si="4"/>
-        <v>36.552532022353233</v>
+        <v>35.19674303381791</v>
       </c>
     </row>
     <row r="264" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -22012,7 +22086,7 @@
         <v>46235</v>
       </c>
       <c r="B264" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C264" s="9" t="s">
         <v>171</v>
@@ -22027,11 +22101,11 @@
         <v>57.2</v>
       </c>
       <c r="G264" s="17">
-        <v>6317</v>
+        <v>6671</v>
       </c>
       <c r="H264" s="15">
         <f t="shared" si="4"/>
-        <v>34.81879564558357</v>
+        <v>36.770015157778694</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -22039,7 +22113,7 @@
         <v>46266</v>
       </c>
       <c r="B265" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C265" s="9" t="s">
         <v>172</v>
@@ -22054,11 +22128,11 @@
         <v>102.7</v>
       </c>
       <c r="G265" s="17">
-        <v>6100</v>
+        <v>6009</v>
       </c>
       <c r="H265" s="15">
         <f t="shared" si="4"/>
-        <v>19.827146288585737</v>
+        <v>19.531364270182248</v>
       </c>
     </row>
     <row r="266" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -22066,7 +22140,7 @@
         <v>46266</v>
       </c>
       <c r="B266" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C266" s="9" t="s">
         <v>172</v>
@@ -22081,11 +22155,11 @@
         <v>72.099999999999994</v>
       </c>
       <c r="G266" s="17">
-        <v>4224</v>
+        <v>4315</v>
       </c>
       <c r="H266" s="15">
         <f t="shared" si="4"/>
-        <v>19.36699632742328</v>
+        <v>19.784230386560477</v>
       </c>
     </row>
     <row r="267" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -22579,7 +22653,7 @@
         <v>46266</v>
       </c>
       <c r="B285" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C285" s="9" t="s">
         <v>171</v>
@@ -22594,11 +22668,11 @@
         <v>51.1</v>
       </c>
       <c r="G285" s="17">
-        <v>11023</v>
+        <v>10611</v>
       </c>
       <c r="H285" s="15">
         <f t="shared" si="4"/>
-        <v>40.167330474042281</v>
+        <v>38.666020471746585</v>
       </c>
     </row>
     <row r="286" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -22606,7 +22680,7 @@
         <v>46266</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C286" s="9" t="s">
         <v>171</v>
@@ -22621,11 +22695,11 @@
         <v>41.5</v>
       </c>
       <c r="G286" s="17">
-        <v>7288</v>
+        <v>7700</v>
       </c>
       <c r="H286" s="15">
         <f t="shared" si="4"/>
-        <v>38.782667000143675</v>
+        <v>40.975100974355968</v>
       </c>
     </row>
     <row r="287" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -22633,7 +22707,7 @@
         <v>46296</v>
       </c>
       <c r="B287" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C287" s="9" t="s">
         <v>172</v>
@@ -22648,11 +22722,11 @@
         <v>82</v>
       </c>
       <c r="G287" s="17">
-        <v>4804</v>
+        <v>4710</v>
       </c>
       <c r="H287" s="15">
         <f t="shared" si="4"/>
-        <v>19.964426417540771</v>
+        <v>19.573781937264158</v>
       </c>
     </row>
     <row r="288" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -22660,7 +22734,7 @@
         <v>46296</v>
       </c>
       <c r="B288" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C288" s="9" t="s">
         <v>172</v>
@@ -22675,11 +22749,11 @@
         <v>85.6</v>
       </c>
       <c r="G288" s="17">
-        <v>5994</v>
+        <v>6089</v>
       </c>
       <c r="H288" s="15">
         <f t="shared" si="4"/>
-        <v>19.613104197479156</v>
+        <v>19.923955865607372</v>
       </c>
     </row>
     <row r="289" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -23173,7 +23247,7 @@
         <v>46296</v>
       </c>
       <c r="B307" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C307" s="9" t="s">
         <v>171</v>
@@ -23188,11 +23262,11 @@
         <v>41.7</v>
       </c>
       <c r="G307" s="17">
-        <v>11783</v>
+        <v>11467</v>
       </c>
       <c r="H307" s="15">
         <f t="shared" si="4"/>
-        <v>35.950195112872571</v>
+        <v>34.98607208345156</v>
       </c>
     </row>
     <row r="308" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -23200,7 +23274,7 @@
         <v>46296</v>
       </c>
       <c r="B308" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C308" s="9" t="s">
         <v>171</v>
@@ -23215,11 +23289,11 @@
         <v>29.5</v>
       </c>
       <c r="G308" s="17">
-        <v>4640</v>
+        <v>4956</v>
       </c>
       <c r="H308" s="15">
         <f t="shared" si="4"/>
-        <v>34.78573784748253</v>
+        <v>37.154766545716257</v>
       </c>
     </row>
     <row r="309" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -23227,7 +23301,7 @@
         <v>46327</v>
       </c>
       <c r="B309" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C309" s="9" t="s">
         <v>172</v>
@@ -23242,11 +23316,11 @@
         <v>83.8</v>
       </c>
       <c r="G309" s="17">
-        <v>5844</v>
+        <v>5765</v>
       </c>
       <c r="H309" s="15">
         <f t="shared" si="4"/>
-        <v>19.564256732327223</v>
+        <v>19.299784404836831</v>
       </c>
     </row>
     <row r="310" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -23254,7 +23328,7 @@
         <v>46327</v>
       </c>
       <c r="B310" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C310" s="9" t="s">
         <v>172</v>
@@ -23269,11 +23343,11 @@
         <v>44.3</v>
       </c>
       <c r="G310" s="17">
-        <v>3969</v>
+        <v>4047</v>
       </c>
       <c r="H310" s="15">
         <f t="shared" si="4"/>
-        <v>18.865682425302545</v>
+        <v>19.236436577273722</v>
       </c>
     </row>
     <row r="311" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -23767,7 +23841,7 @@
         <v>46327</v>
       </c>
       <c r="B329" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C329" s="9" t="s">
         <v>171</v>
@@ -23782,11 +23856,11 @@
         <v>34.1</v>
       </c>
       <c r="G329" s="17">
-        <v>7922</v>
+        <v>7605</v>
       </c>
       <c r="H329" s="15">
         <f t="shared" si="5"/>
-        <v>36.983263695992157</v>
+        <v>35.503372937139659</v>
       </c>
     </row>
     <row r="330" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -23794,7 +23868,7 @@
         <v>46327</v>
       </c>
       <c r="B330" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C330" s="9" t="s">
         <v>171</v>
@@ -23809,11 +23883,11 @@
         <v>61</v>
       </c>
       <c r="G330" s="17">
-        <v>6033</v>
+        <v>6351</v>
       </c>
       <c r="H330" s="15">
         <f t="shared" si="5"/>
-        <v>35.725917723205562</v>
+        <v>37.609034221793223</v>
       </c>
     </row>
     <row r="331" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -23821,7 +23895,7 @@
         <v>46357</v>
       </c>
       <c r="B331" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C331" s="9" t="s">
         <v>172</v>
@@ -23836,11 +23910,11 @@
         <v>74.8</v>
       </c>
       <c r="G331" s="17">
-        <v>5897</v>
+        <v>5799</v>
       </c>
       <c r="H331" s="15">
         <f t="shared" si="5"/>
-        <v>19.360706007498706</v>
+        <v>19.038957798454295</v>
       </c>
     </row>
     <row r="332" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -23848,7 +23922,7 @@
         <v>46357</v>
       </c>
       <c r="B332" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C332" s="9" t="s">
         <v>172</v>
@@ -23863,11 +23937,11 @@
         <v>88.4</v>
       </c>
       <c r="G332" s="17">
-        <v>5459</v>
+        <v>5556</v>
       </c>
       <c r="H332" s="15">
         <f t="shared" si="5"/>
-        <v>19.169115917143348</v>
+        <v>19.509728528237488</v>
       </c>
     </row>
     <row r="333" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -24361,7 +24435,7 @@
         <v>46357</v>
       </c>
       <c r="B351" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C351" s="9" t="s">
         <v>171</v>
@@ -24376,11 +24450,11 @@
         <v>23.5</v>
       </c>
       <c r="G351" s="17">
-        <v>5485</v>
+        <v>5191</v>
       </c>
       <c r="H351" s="15">
         <f t="shared" si="5"/>
-        <v>37.336292101178969</v>
+        <v>35.335039616630816</v>
       </c>
     </row>
     <row r="352" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -24388,7 +24462,7 @@
         <v>46357</v>
       </c>
       <c r="B352" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C352" s="9" t="s">
         <v>171</v>
@@ -24403,11 +24477,11 @@
         <v>63.8</v>
       </c>
       <c r="G352" s="17">
-        <v>7721</v>
+        <v>8015</v>
       </c>
       <c r="H352" s="15">
         <f t="shared" si="5"/>
-        <v>36.386342750771696</v>
+        <v>37.771860788425741</v>
       </c>
     </row>
   </sheetData>
@@ -24449,88 +24523,88 @@
   <sheetData>
     <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>104</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q4" s="8" t="s">
         <v>14</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>168</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E5" s="13">
         <f>IF(A5="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C5&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -24570,16 +24644,16 @@
         <v>Alta</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R5" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S5" s="18">
         <f t="shared" ref="S5:S20" si="6">IF(A5="","",IF(C5="—",0,LEN(C5)-LEN(SUBSTITUTE(C5,";",""))+1))</f>
@@ -24592,16 +24666,16 @@
     </row>
     <row r="6" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>168</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E6" s="13">
         <f>IF(A6="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C6&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -24641,16 +24715,16 @@
         <v>Média</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P6" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R6" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S6" s="18">
         <f t="shared" si="6"/>
@@ -24663,16 +24737,16 @@
     </row>
     <row r="7" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E7" s="13">
         <f>IF(A7="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C7&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -24712,16 +24786,16 @@
         <v>Alta</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="S7" s="18">
         <f t="shared" si="6"/>
@@ -24734,16 +24808,16 @@
     </row>
     <row r="8" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>168</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E8" s="13">
         <f>IF(A8="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C8&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -24783,16 +24857,16 @@
         <v>Média</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R8" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="S8" s="18">
         <f t="shared" si="6"/>
@@ -24805,16 +24879,16 @@
     </row>
     <row r="9" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>167</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E9" s="13">
         <f>IF(A9="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C9&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -24854,13 +24928,13 @@
         <v>Alta</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P9" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="R9" s="9"/>
       <c r="S9" s="18">
@@ -24874,16 +24948,16 @@
     </row>
     <row r="10" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>167</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E10" s="13">
         <f>IF(A10="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C10&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -24923,13 +24997,13 @@
         <v>Alta</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="R10" s="9"/>
       <c r="S10" s="18">
@@ -24943,16 +25017,16 @@
     </row>
     <row r="11" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>168</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E11" s="13">
         <f>IF(A11="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C11&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -24992,16 +25066,16 @@
         <v>Média</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="R11" s="9" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="S11" s="18">
         <f t="shared" si="6"/>
@@ -25014,16 +25088,16 @@
     </row>
     <row r="12" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>169</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E12" s="13">
         <f>IF(A12="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C12&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -25063,16 +25137,16 @@
         <v>Média</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P12" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R12" s="9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="S12" s="18">
         <f t="shared" si="6"/>
@@ -25085,16 +25159,16 @@
     </row>
     <row r="13" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>169</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E13" s="13">
         <f>IF(A13="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C13&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -25134,16 +25208,16 @@
         <v>Média</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="R13" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="S13" s="18">
         <f t="shared" si="6"/>
@@ -25156,16 +25230,16 @@
     </row>
     <row r="14" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>169</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E14" s="13">
         <f>IF(A14="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C14&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -25205,13 +25279,13 @@
         <v>Média</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P14" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="R14" s="9"/>
       <c r="S14" s="18">
@@ -25225,16 +25299,16 @@
     </row>
     <row r="15" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>170</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E15" s="13">
         <f>IF(A15="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C15&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -25274,13 +25348,13 @@
         <v>Baixa</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="R15" s="9"/>
       <c r="S15" s="18">
@@ -25294,16 +25368,16 @@
     </row>
     <row r="16" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E16" s="13">
         <f>IF(A16="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C16&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -25343,16 +25417,16 @@
         <v>Baixa</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P16" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="R16" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="S16" s="18">
         <f t="shared" si="6"/>
@@ -25365,16 +25439,16 @@
     </row>
     <row r="17" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>170</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E17" s="13">
         <f>IF(A17="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C17&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -25414,13 +25488,13 @@
         <v>Média</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="R17" s="9"/>
       <c r="S17" s="18">
@@ -25434,16 +25508,16 @@
     </row>
     <row r="18" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>164</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E18" s="13">
         <f>IF(A18="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C18&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -25483,16 +25557,16 @@
         <v>Média</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="P18" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="R18" s="9" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="S18" s="18">
         <f t="shared" si="6"/>
@@ -25505,16 +25579,16 @@
     </row>
     <row r="19" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E19" s="13">
         <f>IF(A19="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C19&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -25554,16 +25628,16 @@
         <v>Alta</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="R19" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="S19" s="18">
         <f t="shared" si="6"/>
@@ -25576,16 +25650,16 @@
     </row>
     <row r="20" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E20" s="13">
         <f>IF(A20="","",SUMPRODUCT(ISNUMBER(SEARCH(tbl_usos[ID_Uso]&amp;";",C20&amp;";"))*tbl_usos[kWh_12m]))</f>
@@ -25625,16 +25699,16 @@
         <v>Baixa</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="S20" s="18">
         <f t="shared" si="6"/>
